--- a/reports/jobs_2026-10-25.xlsx
+++ b/reports/jobs_2026-10-25.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3237,17 +3237,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Gen AI Engineer-AWS</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/san-jose-ca/R-110306-1/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3280,17 +3280,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/san-jose-ca/R-110382-1/</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/austin-tx/R-110306/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>GenAI-Engineer</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/austin-tx/R-110379/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3409,17 +3409,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/san-jose-ca/R-110379-1/</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3495,17 +3495,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/seattle-wa/R-110379-2/</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3538,17 +3538,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3556,7 +3556,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3564,12 +3568,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/seattle-wa/R-110306-2/</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3581,17 +3585,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3599,7 +3603,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3607,12 +3615,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3624,17 +3632,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-AWS</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3642,7 +3650,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3650,12 +3662,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3667,17 +3679,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3685,7 +3697,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3693,12 +3709,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3710,17 +3726,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3736,12 +3752,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3753,12 +3769,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3779,12 +3795,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3796,12 +3812,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3814,7 +3830,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3822,12 +3842,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3839,17 +3859,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3857,7 +3877,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -3865,12 +3889,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3882,12 +3906,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3908,12 +3932,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3925,17 +3949,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3945,7 +3969,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3955,12 +3979,12 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3972,17 +3996,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3990,11 +4014,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4002,12 +4022,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4019,12 +4039,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4037,11 +4057,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4049,12 +4065,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4066,17 +4082,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4084,11 +4100,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4096,12 +4108,12 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4113,12 +4125,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4131,7 +4143,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4139,12 +4155,12 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4156,17 +4172,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4174,7 +4190,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4182,12 +4202,12 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4199,17 +4219,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4219,7 +4239,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4229,12 +4249,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4246,17 +4266,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4266,7 +4286,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4276,12 +4296,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4293,17 +4313,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4311,7 +4331,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4319,12 +4343,12 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4336,17 +4360,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4356,7 +4380,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4366,12 +4390,12 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4383,17 +4407,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4409,12 +4433,12 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4426,17 +4450,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4444,7 +4468,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4452,12 +4480,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4469,17 +4497,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4487,7 +4515,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4495,12 +4527,12 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4512,17 +4544,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4532,7 +4564,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4542,12 +4574,12 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4559,12 +4591,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4577,11 +4609,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4589,12 +4617,12 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4606,12 +4634,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4626,7 +4654,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4636,12 +4664,12 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4653,17 +4681,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4673,7 +4701,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4683,12 +4711,12 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4700,17 +4728,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4720,7 +4748,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4730,12 +4758,12 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4747,27 +4775,27 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4777,12 +4805,12 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4794,12 +4822,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4812,7 +4840,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4820,12 +4852,12 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4837,17 +4869,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4855,11 +4887,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4867,12 +4895,12 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4884,12 +4912,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4902,11 +4930,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4914,12 +4938,12 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4931,17 +4955,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4949,11 +4973,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -4961,12 +4981,12 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -4978,17 +4998,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5004,12 +5024,12 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5021,17 +5041,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5039,11 +5059,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5051,12 +5067,12 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5068,17 +5084,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -5088,7 +5104,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5098,12 +5114,12 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5115,17 +5131,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5135,7 +5151,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5145,12 +5161,12 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5162,29 +5178,25 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5192,12 +5204,12 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5209,17 +5221,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5227,11 +5239,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5239,12 +5247,12 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5256,12 +5264,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5274,7 +5282,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5282,12 +5294,12 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5299,12 +5311,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5317,7 +5329,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5325,12 +5341,12 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5342,17 +5358,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5360,7 +5376,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5368,12 +5388,12 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5385,12 +5405,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Zscaler India</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Escalation Engineer</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5403,7 +5423,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
@@ -5411,12 +5435,12 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5425,419 +5449,8 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>AI Animator</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>QA / SDET</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>SirionLabs</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Intern- Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sirionlabs.com/careers/</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Zscaler India</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Escalation Engineer</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, IND</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I119"/>
+  <autoFilter ref="A1:I110"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5948,15 +5561,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5968,7 +5572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5996,35 +5600,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Cuemath</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cuemath</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.cuemath.com/careers/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6033,18 +5617,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6053,18 +5637,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6073,6 +5657,26 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tonbo Imaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.tonboimaging.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.tonboimaging.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -6116,15 +5720,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Capillary Technologies</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.capillarytech.com/careers/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6133,26 +5757,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -6236,55 +5840,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FirstCry</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.firstcry.com/careers</t>
+          <t>https://www.zomato.com/careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Zomato</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.zomato.com/careers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -6293,18 +5857,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6313,18 +5877,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -6333,18 +5897,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -6353,18 +5917,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
